--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>14.62019968032837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>15.12493872642517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>26.79174065589905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>11.48440098762512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>9.209387302398682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>6.100962400436401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>15.73788404464722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.820160865783691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>8.674446821212769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>11.96173334121704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>20.14616942405701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1944,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>21.16209983825684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>4.595532894134521</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2002,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>14.29761075973511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2031,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>8.612384796142578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2060,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>7.93376350402832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>8.109052181243896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>31.78124666213989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2147,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>6.631600379943848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>12.81981778144836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>6.697922945022583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>15.94959425926208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>24.83627223968506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>11.5198667049408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>10.67841005325317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2350,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>22.60945463180542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>7.332891464233398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>16.41543197631836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>3.705526351928711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>10.67870354652405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>7.415929079055786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>17.59847736358643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>6.342408895492554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>10.00116634368896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>23.15612936019897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2640,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>8.654062509536743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>6.460486888885498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2698,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>10.88451075553894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>10.59368681907654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>14.02832174301147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>4.010684490203857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>6.353055715560913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>4.471264839172363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>8.75069785118103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>4.770550966262817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>4.995634794235229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2959,7 +2959,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>10.81858611106873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2988,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>6.652421474456787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>16.49416828155518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>4.982126951217651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>10.2285590171814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>5.898650884628296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>3.737233638763428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>14.71447157859802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>14.7514545917511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3220,7 +3220,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>16.66955733299255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>15.37400054931641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>11.19822382926941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3307,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>6.096821784973145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>3.754865646362305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3365,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>4.750461101531982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>19.02870225906372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3423,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>7.836593627929688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>7.260666608810425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>7.104093074798584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>6.859151124954224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3539,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>4.974404335021973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3568,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>27.30562353134155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3597,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>6.350167751312256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>21.8017373085022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3655,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>5.975618839263916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3684,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>9.378146409988403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3713,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>12.98688077926636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>11.09954619407654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>4.203003644943237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>7.022656440734863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3829,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>12.03956651687622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>8.268237113952637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>5.890929222106934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>14.48897361755371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3945,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>8.515938282012939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3974,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>5.472244739532471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>13.26967549324036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4032,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>9.874669075012207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>21.52029395103455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4090,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>10.23970007896423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4119,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>19.45517492294312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>12.61906933784485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4177,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>28.17358756065369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>4.928216218948364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>12.810791015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4264,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>5.679142475128174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -4293,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="I94">
-        <v>22.72391414642334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -4322,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>5.168132543563843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -4351,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>14.45226979255676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -4380,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>10.69643187522888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4409,7 +4409,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>15.92841958999634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4438,7 +4438,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <v>6.186078310012817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>32.97755789756775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>11.35402274131775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>19.76348876953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -4554,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>10.95795655250549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -4583,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="I104">
-        <v>11.79866623878479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -4612,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>34.10459804534912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>80.85759902000427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>10.60815906524658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>5.745544910430908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>4.955566644668579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>44.87112379074097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>4.538486480712891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4815,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>14.59123945236206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4844,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>9.859512805938721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>9.042544603347778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4902,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>9.543981075286865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>24.69924163818359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>7.185946702957153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4989,7 +4989,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>10.14824557304382</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>8.952752351760864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5047,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>8.815158843994141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5076,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>20.48761057853699</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
